--- a/results/02_taxa_assemblage/tables/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/tables/reference_taxa_clusters.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0.8019817499587525</v>
@@ -581,17 +581,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>010B</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5385269277308715</v>
       </c>
       <c r="D3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.517161661945792</v>
       </c>
       <c r="E3" t="n">
         <v>3.203426503814917e-16</v>
@@ -600,10 +600,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.874765816126109</v>
       </c>
       <c r="H3" t="n">
-        <v>5.357552004618084</v>
+        <v>5.573081656582537</v>
       </c>
       <c r="I3" t="n">
         <v>3.203426503814917e-16</v>
@@ -615,16 +615,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9297738636749643</v>
       </c>
       <c r="M3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5385269277308715</v>
       </c>
       <c r="N3" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O3" t="n">
-        <v>5.930737337562887</v>
+        <v>0.5385269277308715</v>
       </c>
       <c r="P3" t="n">
         <v>3.203426503814917e-16</v>
@@ -639,14 +639,14 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>011A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="D4" t="n">
         <v>3.203426503814917e-16</v>
@@ -655,16 +655,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="G4" t="n">
-        <v>4.402534852460246</v>
+        <v>5.714661819801716</v>
       </c>
       <c r="H4" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8042755291256324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J4" t="n">
         <v>3.203426503814917e-16</v>
@@ -679,10 +679,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>6.289812447870645</v>
+        <v>4.968230419506606</v>
       </c>
       <c r="O4" t="n">
-        <v>1.518873310263384</v>
+        <v>3.713829095368272</v>
       </c>
       <c r="P4" t="n">
         <v>3.203426503814917e-16</v>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>018A</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -707,7 +707,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7862933065297747</v>
+        <v>4.08545281648648</v>
       </c>
       <c r="E5" t="n">
         <v>3.203426503814917e-16</v>
@@ -716,34 +716,34 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G5" t="n">
-        <v>4.142957953842043</v>
+        <v>1.751405406024398</v>
       </c>
       <c r="H5" t="n">
-        <v>4.362134417282382</v>
+        <v>6.294892591337625</v>
       </c>
       <c r="I5" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.984982964359276</v>
       </c>
       <c r="K5" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L5" t="n">
-        <v>4.362134417282382</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6705829262744399</v>
       </c>
       <c r="N5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6705829262744399</v>
       </c>
       <c r="O5" t="n">
-        <v>2.602281976921183</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P5" t="n">
-        <v>5.300335979246591</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q5" t="n">
         <v>3.203426503814917e-16</v>
@@ -755,75 +755,75 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1.330645311988472</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>3.713829095368272</v>
+        <v>3.55019708256048</v>
       </c>
       <c r="E6" t="n">
-        <v>2.010888316142736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F6" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>5.036423408249874</v>
+        <v>2.192645077942396</v>
       </c>
       <c r="H6" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.988684686772165</v>
       </c>
       <c r="I6" t="n">
-        <v>3.100264123473429</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J6" t="n">
-        <v>4.896653486982127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K6" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L6" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.478047296804644</v>
       </c>
       <c r="M6" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.025535092107138</v>
       </c>
       <c r="N6" t="n">
-        <v>2.010888316142736</v>
+        <v>1.478047296804644</v>
       </c>
       <c r="O6" t="n">
-        <v>3.334984247712809</v>
+        <v>3.025535092107138</v>
       </c>
       <c r="P6" t="n">
-        <v>2.010888316142736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q6" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.668378508908793</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.045233364735362</v>
       </c>
       <c r="E7" t="n">
         <v>3.203426503814917e-16</v>
@@ -832,10 +832,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>5.672425341971495</v>
+        <v>1.264986512097531</v>
       </c>
       <c r="H7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.309004397742273</v>
       </c>
       <c r="I7" t="n">
         <v>3.203426503814917e-16</v>
@@ -847,16 +847,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.68511366861321</v>
       </c>
       <c r="M7" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>2.584962500721157</v>
+        <v>0.8579075100879084</v>
       </c>
       <c r="O7" t="n">
-        <v>5.523561956057013</v>
+        <v>1.471200911255877</v>
       </c>
       <c r="P7" t="n">
         <v>3.203426503814917e-16</v>
@@ -871,17 +871,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>033ABC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>1.350716518311987</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.5556469338966</v>
       </c>
       <c r="E8" t="n">
         <v>3.203426503814917e-16</v>
@@ -890,7 +890,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>5.350259665639975</v>
+        <v>5.635374126367335</v>
       </c>
       <c r="H8" t="n">
         <v>3.203426503814917e-16</v>
@@ -899,47 +899,47 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.76955288934522</v>
       </c>
       <c r="K8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7194478329081769</v>
       </c>
       <c r="L8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.197301440373618</v>
       </c>
       <c r="M8" t="n">
-        <v>0.331588205937932</v>
+        <v>0.8969065070358966</v>
       </c>
       <c r="N8" t="n">
-        <v>1.196600538156653</v>
+        <v>0.5170584362193528</v>
       </c>
       <c r="O8" t="n">
-        <v>5.78825675019676</v>
+        <v>5.368130103004817</v>
       </c>
       <c r="P8" t="n">
-        <v>1.024030069363076</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.331588205937932</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.350716518311987</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="E9" t="n">
         <v>3.203426503814917e-16</v>
@@ -948,13 +948,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G9" t="n">
-        <v>1.268105395381216</v>
+        <v>2.526545814495834</v>
       </c>
       <c r="H9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.13026410847607</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J9" t="n">
         <v>3.203426503814917e-16</v>
@@ -966,13 +966,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M9" t="n">
-        <v>3.914995645245574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>6.369643421843278</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.689831618575111</v>
       </c>
       <c r="P9" t="n">
         <v>3.203426503814917e-16</v>
@@ -981,17 +981,17 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.268105395381216</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1006,7 +1006,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G10" t="n">
-        <v>4.876972617710485</v>
+        <v>6.438197784198078</v>
       </c>
       <c r="H10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1027,25 +1027,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.02033099828571</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O10" t="n">
-        <v>6.101935543140568</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7268502500741482</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R10" t="n">
-        <v>0.284917523732244</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>043ABC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1055,46 +1055,46 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75304380217978</v>
+        <v>5.487806189871804</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5556469338966</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F11" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65968839300624</v>
+        <v>0.4650147144136517</v>
       </c>
       <c r="H11" t="n">
-        <v>3.844191690237976</v>
+        <v>5.739616035545461</v>
       </c>
       <c r="I11" t="n">
-        <v>1.926653850429949</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J11" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K11" t="n">
-        <v>2.52139737194369</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L11" t="n">
-        <v>4.880111264492919</v>
+        <v>1.169707246013332</v>
       </c>
       <c r="M11" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.615725305729703</v>
       </c>
       <c r="N11" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O11" t="n">
-        <v>4.271945938382821</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>4.083066611213009</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5170584362193528</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1103,53 +1103,53 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9047272710591775</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5618788876081152</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F12" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G12" t="n">
-        <v>5.985977433133131</v>
+        <v>0.09368399654834478</v>
       </c>
       <c r="H12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.643280158288579</v>
       </c>
       <c r="I12" t="n">
-        <v>1.947532580105865</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J12" t="n">
-        <v>1.538419914784126</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K12" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L12" t="n">
-        <v>1.947532580105865</v>
+        <v>0.09368399654834478</v>
       </c>
       <c r="M12" t="n">
-        <v>2.115477217419936</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>3.328781765928425</v>
+        <v>0.04760230704818257</v>
       </c>
       <c r="O12" t="n">
-        <v>4.142957953842043</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5618788876081152</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1161,17 +1161,17 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.907772708164823</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>2.223337521298769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1180,13 +1180,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>3.346859325384784</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H13" t="n">
-        <v>4.786884066556411</v>
+        <v>6.643254941572279</v>
       </c>
       <c r="I13" t="n">
-        <v>3.471414204472197</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1195,22 +1195,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L13" t="n">
-        <v>4.404868132997189</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M13" t="n">
-        <v>2.482114093129406</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>1.503278703127448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O13" t="n">
-        <v>4.204077523956366</v>
+        <v>1.029747343394052</v>
       </c>
       <c r="P13" t="n">
-        <v>1.503278703127448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.503278703127448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1219,90 +1219,90 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1.908283830908385</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1952562913989341</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="E14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.02267182631393</v>
       </c>
       <c r="F14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>5.392815161283227</v>
+        <v>5.887992562015887</v>
       </c>
       <c r="H14" t="n">
-        <v>1.52810016376548</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5208321633014408</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9027027986450852</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7526899464592227</v>
       </c>
       <c r="L14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3672089741882289</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>1.375291320486087</v>
+        <v>1.244803668756707</v>
       </c>
       <c r="O14" t="n">
-        <v>5.626608427361777</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="P14" t="n">
-        <v>1.110644063683993</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.204358498506187</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1952562913989341</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>1.025928464990526</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D15" t="n">
-        <v>2.744049522542173</v>
+        <v>2.712718047919529</v>
       </c>
       <c r="E15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="F15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>3.294001658435625</v>
+        <v>2.712718047919529</v>
       </c>
       <c r="H15" t="n">
-        <v>3.632147644270419</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.844254504869133</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1311,19 +1311,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L15" t="n">
-        <v>5.259487160731418</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M15" t="n">
-        <v>4.749895472819714</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.317915032380739</v>
       </c>
       <c r="O15" t="n">
-        <v>2.210059327853142</v>
+        <v>2.712718047919529</v>
       </c>
       <c r="P15" t="n">
-        <v>2.210059327853142</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1335,32 +1335,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9928402084271342</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5801932565732844</v>
+        <v>3.721932779208732</v>
       </c>
       <c r="F16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>4.07395594291159</v>
+        <v>6.304671300699757</v>
       </c>
       <c r="H16" t="n">
-        <v>2.158772140503586</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.235090048108769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1369,22 +1369,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="M16" t="n">
-        <v>1.797115737552766</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.827323338290201</v>
       </c>
       <c r="O16" t="n">
-        <v>5.963153611563069</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5801932565732844</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.894457614762477</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,56 +1393,56 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>1.256339753259786</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E17" t="n">
-        <v>4.565913046718168</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>5.317915032380738</v>
+        <v>6.051070184214275</v>
       </c>
       <c r="H17" t="n">
-        <v>1.256339753259786</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I17" t="n">
-        <v>3.358854663885719</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>1.917537839808027</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O17" t="n">
-        <v>4.448460500816294</v>
+        <v>5.157604729806445</v>
       </c>
       <c r="P17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.256339753259786</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1451,29 +1451,29 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3263154121283017</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08875461424297566</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G18" t="n">
-        <v>5.998740754099797</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.339850002884624</v>
       </c>
       <c r="I18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1488,19 +1488,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6517437797578886</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>1.473345203336181</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O18" t="n">
-        <v>5.142716125671646</v>
+        <v>4.392317422778761</v>
       </c>
       <c r="P18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.08875461424297566</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1509,32 +1509,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>5.144054104230877</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1543,22 +1543,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>1.85065345479636</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M19" t="n">
-        <v>1.127523751722153</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>1.410757771901608</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O19" t="n">
-        <v>5.889810299081591</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,29 +1567,29 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4287006624855133</v>
+        <v>2.605196984461211</v>
       </c>
       <c r="D20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E20" t="n">
-        <v>2.365202356081421</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F20" t="n">
-        <v>2.040607317244977</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>5.894272313010426</v>
+        <v>3.244061423481349</v>
       </c>
       <c r="H20" t="n">
-        <v>1.44895580751278</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1607,10 +1607,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>3.370521499177415</v>
+        <v>5.64825093183208</v>
       </c>
       <c r="O20" t="n">
-        <v>4.575153180193171</v>
+        <v>5.258825506031243</v>
       </c>
       <c r="P20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1625,29 +1625,29 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4989892776113035</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8690393221168372</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G21" t="n">
-        <v>5.38919132179204</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.426264754702098</v>
       </c>
       <c r="I21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1665,10 +1665,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>1.163285804079277</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O21" t="n">
-        <v>5.848286675010258</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,38 +1683,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D22" t="n">
-        <v>1.888578717331577</v>
+        <v>2.676761810284823</v>
       </c>
       <c r="E22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8717455093275589</v>
       </c>
       <c r="F22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.500738592794211</v>
       </c>
       <c r="G22" t="n">
-        <v>4.662451872030237</v>
+        <v>6.481908269132582</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>1.597901556428655</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.411291210388779</v>
       </c>
       <c r="K22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.500738592794211</v>
       </c>
       <c r="L22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1723,56 +1723,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.888578717331577</v>
+        <v>0.500738592794211</v>
       </c>
       <c r="O22" t="n">
-        <v>6.056161680855508</v>
+        <v>1.803072654025182</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.233490130219779</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8654578766211725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F23" t="n">
-        <v>1.902932582039835</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>4.254154983721236</v>
+        <v>5.930737337562887</v>
       </c>
       <c r="H23" t="n">
-        <v>5.183584401348678</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I23" t="n">
-        <v>3.022063735665987</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J23" t="n">
-        <v>2.695871814459378</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.392317422778761</v>
       </c>
       <c r="L23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1781,35 +1781,35 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>2.273699814391163</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O23" t="n">
-        <v>4.42947839653567</v>
+        <v>4.392317422778761</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.273699814391163</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.529467388129453</v>
       </c>
       <c r="D24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.776898533069642</v>
       </c>
       <c r="E24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1818,10 +1818,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G24" t="n">
-        <v>6.131155431277737</v>
+        <v>3.623018726983232</v>
       </c>
       <c r="H24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.255073120131111</v>
       </c>
       <c r="I24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1839,10 +1839,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.203555779323592</v>
       </c>
       <c r="O24" t="n">
-        <v>4.995895601667264</v>
+        <v>4.443256343088573</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1857,38 +1857,38 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1.304854581528421</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="D25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E25" t="n">
-        <v>2.584962500721157</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="F25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G25" t="n">
-        <v>6.082462160191973</v>
+        <v>4.372118352313833</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6674246609131292</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3719687773869582</v>
+        <v>1.970746195024886</v>
       </c>
       <c r="J25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="L25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1897,16 +1897,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.745427172914402</v>
+        <v>4.881035788519983</v>
       </c>
       <c r="O25" t="n">
-        <v>4.527247002864868</v>
+        <v>5.576380898876536</v>
       </c>
       <c r="P25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.304854581528421</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1915,11 +1915,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1928,22 +1928,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E26" t="n">
-        <v>2.508772937544713</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G26" t="n">
-        <v>5.871125674841771</v>
+        <v>4.886132035441721</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3183614798671702</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="K26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1952,19 +1952,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.861530062208643</v>
       </c>
       <c r="O26" t="n">
-        <v>5.172396639944554</v>
+        <v>3.48595249488999</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9910668752299923</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1973,11 +1973,11 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>3.203426503814917e-16</v>
@@ -1989,19 +1989,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F27" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>5.853451336647058</v>
+        <v>4.402534852460246</v>
       </c>
       <c r="H27" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8042755291256324</v>
       </c>
       <c r="J27" t="n">
-        <v>2.212993723334198</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2013,47 +2013,47 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>2.740240726199067</v>
+        <v>6.289812447870645</v>
       </c>
       <c r="O27" t="n">
-        <v>5.056268219646745</v>
+        <v>1.518873310263384</v>
       </c>
       <c r="P27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2954558835261716</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>2.321928094887362</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D28" t="n">
-        <v>2.321928094887362</v>
+        <v>3.582027209696609</v>
       </c>
       <c r="E28" t="n">
-        <v>1.222392421336448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G28" t="n">
-        <v>5.309855262586788</v>
+        <v>0.6868421147403698</v>
       </c>
       <c r="H28" t="n">
-        <v>1.874469117916141</v>
+        <v>6.452617933046574</v>
       </c>
       <c r="I28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2068,19 +2068,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M28" t="n">
-        <v>1.874469117916141</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="O28" t="n">
-        <v>4.92283213947754</v>
+        <v>0.6868421147403698</v>
       </c>
       <c r="P28" t="n">
-        <v>4.087462841250339</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.222392421336448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2089,90 +2089,90 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="D29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.441858732844736</v>
       </c>
       <c r="E29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="F29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="G29" t="n">
-        <v>3.996929781686806</v>
+        <v>4.592516646115072</v>
       </c>
       <c r="H29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.3657782510295</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7486948867483135</v>
+        <v>1.186447986673725</v>
       </c>
       <c r="J29" t="n">
-        <v>1.604458676346953</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9685979008608663</v>
       </c>
       <c r="M29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>1.239119507741897</v>
+        <v>3.28864350317529</v>
       </c>
       <c r="O29" t="n">
-        <v>5.792380848016275</v>
+        <v>4.648634242809477</v>
       </c>
       <c r="P29" t="n">
-        <v>0.7486948867483135</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.373501439850122</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R29" t="n">
-        <v>2.832373382094444</v>
+        <v>0.5641038958234921</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="E30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.195861790625938</v>
       </c>
       <c r="F30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G30" t="n">
-        <v>6.086383652788929</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="H30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I30" t="n">
-        <v>2.501061243112211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2187,44 +2187,44 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>2.267104070142841</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="O30" t="n">
-        <v>4.52568669140555</v>
+        <v>6.137252569345645</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.430239905922514</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8855412754150851</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4378774756369554</v>
       </c>
       <c r="F31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G31" t="n">
-        <v>3.598259323334614</v>
+        <v>1.045323990509491</v>
       </c>
       <c r="H31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2245,16 +2245,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>3.598259323334614</v>
+        <v>3.745382295550968</v>
       </c>
       <c r="O31" t="n">
-        <v>4.53743413063857</v>
+        <v>6.445763325802663</v>
       </c>
       <c r="P31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.506032031499436</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2263,14 +2263,14 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.82797653267369</v>
       </c>
       <c r="D32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2282,10 +2282,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G32" t="n">
-        <v>4.290677160902923</v>
+        <v>1.350716518311988</v>
       </c>
       <c r="H32" t="n">
-        <v>5.454739923312576</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2303,10 +2303,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>3.635588573791124</v>
+        <v>2.285688951456035</v>
       </c>
       <c r="O32" t="n">
-        <v>4.739539537830033</v>
+        <v>6.56679155955111</v>
       </c>
       <c r="P32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2315,41 +2315,41 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R32" t="n">
-        <v>1.280107919192735</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.713829095368272</v>
       </c>
       <c r="E33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="F33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.036423408249874</v>
       </c>
       <c r="H33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I33" t="n">
-        <v>6.08037341646402</v>
+        <v>3.100264123473429</v>
       </c>
       <c r="J33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.896653486982127</v>
       </c>
       <c r="K33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2361,13 +2361,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="O33" t="n">
-        <v>5.101538026462062</v>
+        <v>3.334984247712809</v>
       </c>
       <c r="P33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="Q33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2379,32 +2379,32 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="D34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="F34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.144054104230877</v>
       </c>
       <c r="H34" t="n">
-        <v>5.462819553754064</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I34" t="n">
-        <v>1.445799753049531</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="J34" t="n">
         <v>3.203426503814917e-16</v>
@@ -2413,50 +2413,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.85065345479636</v>
       </c>
       <c r="M34" t="n">
-        <v>1.445799753049531</v>
+        <v>1.127523751722153</v>
       </c>
       <c r="N34" t="n">
-        <v>2.625834782136685</v>
+        <v>1.410757771901608</v>
       </c>
       <c r="O34" t="n">
-        <v>5.149046271766396</v>
+        <v>5.889810299081591</v>
       </c>
       <c r="P34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.625834782136685</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="R34" t="n">
-        <v>3.266140316701616</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4989892776113035</v>
       </c>
       <c r="D35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8690393221168372</v>
       </c>
       <c r="F35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>4.15677962538539</v>
+        <v>5.38919132179204</v>
       </c>
       <c r="H35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2465,7 +2465,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5947435215137417</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2477,10 +2477,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N35" t="n">
-        <v>2.192645077942396</v>
+        <v>1.163285804079277</v>
       </c>
       <c r="O35" t="n">
-        <v>6.29555811169563</v>
+        <v>5.848286675010258</v>
       </c>
       <c r="P35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2489,13 +2489,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R35" t="n">
-        <v>1.339486466271667</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2505,7 +2505,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="E36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2514,13 +2514,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G36" t="n">
-        <v>2.166192282565982</v>
+        <v>4.662451872030237</v>
       </c>
       <c r="H36" t="n">
-        <v>5.828173393565159</v>
+        <v>0.7447429447579256</v>
       </c>
       <c r="I36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.597901556428655</v>
       </c>
       <c r="J36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2535,56 +2535,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>3.825612104325463</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="O36" t="n">
-        <v>4.77381645935647</v>
+        <v>6.056161680855508</v>
       </c>
       <c r="P36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4725885218410026</v>
+        <v>1.233490130219779</v>
       </c>
       <c r="R36" t="n">
-        <v>0.82797653267369</v>
+        <v>0.7447429447579256</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="D37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="F37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G37" t="n">
-        <v>2.366007313171981</v>
+        <v>6.082462160191973</v>
       </c>
       <c r="H37" t="n">
-        <v>3.659279427970584</v>
+        <v>0.6674246609131292</v>
       </c>
       <c r="I37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3719687773869582</v>
       </c>
       <c r="J37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6360019337216219</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2593,16 +2593,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N37" t="n">
-        <v>4.462878920255767</v>
+        <v>1.745427172914402</v>
       </c>
       <c r="O37" t="n">
-        <v>5.991042828457422</v>
+        <v>4.527247002864868</v>
       </c>
       <c r="P37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="R37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2611,11 +2611,11 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2624,19 +2624,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.508772937544713</v>
       </c>
       <c r="F38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G38" t="n">
-        <v>3.797347748702223</v>
+        <v>5.871125674841771</v>
       </c>
       <c r="H38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3183614798671702</v>
       </c>
       <c r="I38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="J38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2648,19 +2648,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="N38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O38" t="n">
-        <v>6.434359193595686</v>
+        <v>5.172396639944554</v>
       </c>
       <c r="P38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.38565369249775</v>
+        <v>0.9910668752299923</v>
       </c>
       <c r="R38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2669,11 +2669,11 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2685,22 +2685,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="G39" t="n">
-        <v>4.612163162004862</v>
+        <v>5.853451336647058</v>
       </c>
       <c r="H39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="I39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.212993723334198</v>
       </c>
       <c r="K39" t="n">
-        <v>2.411694056204474</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2709,35 +2709,35 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6935729986528256</v>
+        <v>2.740240726199067</v>
       </c>
       <c r="O39" t="n">
-        <v>6.132079184757066</v>
+        <v>5.056268219646745</v>
       </c>
       <c r="P39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.794576317336301</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="R39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2954558835261716</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="D40" t="n">
-        <v>3.946466801649578</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2746,19 +2746,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G40" t="n">
-        <v>4.742376604145422</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="H40" t="n">
-        <v>1.341269817188368</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6901908350612248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K40" t="n">
-        <v>1.911015109459704</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2767,35 +2767,35 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N40" t="n">
-        <v>3.350844299056191</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="O40" t="n">
-        <v>5.416765153834561</v>
+        <v>4.53743413063857</v>
       </c>
       <c r="P40" t="n">
-        <v>1.654086861375977</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6901908350612248</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="R40" t="n">
-        <v>1.155097583764673</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4821516951373809</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D41" t="n">
-        <v>2.622632918687211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2804,19 +2804,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>5.780526748697312</v>
+        <v>4.290677160902923</v>
       </c>
       <c r="H41" t="n">
-        <v>1.757429696725922</v>
+        <v>5.454739923312576</v>
       </c>
       <c r="I41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J41" t="n">
-        <v>1.757429696725922</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8428990389152713</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2825,32 +2825,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N41" t="n">
-        <v>3.775936825679039</v>
+        <v>3.635588573791124</v>
       </c>
       <c r="O41" t="n">
-        <v>4.435289923305293</v>
+        <v>4.739539537830033</v>
       </c>
       <c r="P41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4821516951373809</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R41" t="n">
-        <v>1.131244533278253</v>
+        <v>1.280107919192735</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5574817642990493</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2862,16 +2862,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G42" t="n">
-        <v>3.623018726983231</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H42" t="n">
-        <v>5.487612545182457</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3055025469742512</v>
+        <v>6.08037341646402</v>
       </c>
       <c r="J42" t="n">
-        <v>1.272079545436801</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2883,16 +2883,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N42" t="n">
-        <v>4.008481476755091</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O42" t="n">
-        <v>4.789256798126342</v>
+        <v>5.101538026462062</v>
       </c>
       <c r="P42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9585800726200192</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2901,17 +2901,17 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2.813555626621104</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D43" t="n">
-        <v>1.812524024831787</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2920,16 +2920,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G43" t="n">
-        <v>5.062297041796164</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H43" t="n">
-        <v>3.328438136200979</v>
+        <v>5.462819553754064</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5873770536544561</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="J43" t="n">
-        <v>2.465351050405582</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2938,32 +2938,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="N43" t="n">
-        <v>4.072890040163067</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="O43" t="n">
-        <v>4.801387467107483</v>
+        <v>5.149046271766396</v>
       </c>
       <c r="P43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.70545004745549</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="R43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.266140316701616</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2978,7 +2978,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G44" t="n">
-        <v>5.884219765410462</v>
+        <v>3.797347748702223</v>
       </c>
       <c r="H44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2999,16 +2999,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N44" t="n">
-        <v>3.797347748702223</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O44" t="n">
-        <v>4.908441047171919</v>
+        <v>6.434359193595686</v>
       </c>
       <c r="P44" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.38565369249775</v>
       </c>
       <c r="R44" t="n">
         <v>3.203426503814917e-16</v>
@@ -3017,17 +3017,17 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>1.349358265727701</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="D45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.622632918687211</v>
       </c>
       <c r="E45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3036,53 +3036,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G45" t="n">
-        <v>4.616440732194325</v>
+        <v>5.780526748697312</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3891234984260248</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6952767815530165</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="K45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8428990389152713</v>
       </c>
       <c r="L45" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3891234984260248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N45" t="n">
-        <v>1.514796482951849</v>
+        <v>3.775936825679039</v>
       </c>
       <c r="O45" t="n">
-        <v>6.167876379727164</v>
+        <v>4.435289923305293</v>
       </c>
       <c r="P45" t="n">
-        <v>0.9476979983300771</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="R45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.131244533278253</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1.330645311988472</v>
+        <v>0.5574817642990493</v>
       </c>
       <c r="D46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3094,16 +3094,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G46" t="n">
-        <v>5.872231802852783</v>
+        <v>3.623018726983231</v>
       </c>
       <c r="H46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.487612545182457</v>
       </c>
       <c r="I46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3055025469742512</v>
       </c>
       <c r="J46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.272079545436801</v>
       </c>
       <c r="K46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3115,16 +3115,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N46" t="n">
-        <v>3.87148525947732</v>
+        <v>4.008481476755091</v>
       </c>
       <c r="O46" t="n">
-        <v>4.741875508290013</v>
+        <v>4.789256798126342</v>
       </c>
       <c r="P46" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.330645311988472</v>
+        <v>0.9585800726200192</v>
       </c>
       <c r="R46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3133,14 +3133,14 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9585800726200192</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3152,7 +3152,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G47" t="n">
-        <v>4.312369266462518</v>
+        <v>5.872231802852783</v>
       </c>
       <c r="H47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3167,22 +3167,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L47" t="n">
-        <v>2.515253528909752</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M47" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N47" t="n">
-        <v>4.090661722917659</v>
+        <v>3.87148525947732</v>
       </c>
       <c r="O47" t="n">
-        <v>5.917287628211485</v>
+        <v>4.741875508290013</v>
       </c>
       <c r="P47" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="R47" t="n">
         <v>3.203426503814917e-16</v>
